--- a/artfynd/A 25295-2023 artfynd.xlsx
+++ b/artfynd/A 25295-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25295-2023 artfynd.xlsx
+++ b/artfynd/A 25295-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101375901</v>
+        <v>101375839</v>
       </c>
       <c r="B2" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>82</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -731,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451597.2468161641</v>
+        <v>451584</v>
       </c>
       <c r="R2" t="n">
-        <v>6292448.234649378</v>
+        <v>6292466</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,24 +759,14 @@
           <t>2022-06-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-03</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>7 stänglar med knoppar. Barrskog.</t>
+          <t>35 knoppstänglar. Barrskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -809,15 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101375839</v>
+        <v>101375901</v>
       </c>
       <c r="B3" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -865,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451584.2736540178</v>
+        <v>451597</v>
       </c>
       <c r="R3" t="n">
-        <v>6292465.9194583</v>
+        <v>6292448</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -898,24 +878,14 @@
           <t>2022-06-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-03</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>35 knoppstänglar. Barrskog.</t>
+          <t>7 stänglar med knoppar. Barrskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -940,6 +910,125 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>101375928</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ljusandal, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>451700</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6292336</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Agunnaryd</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-06-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-06-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Traktorväg</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25295-2023 artfynd.xlsx
+++ b/artfynd/A 25295-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101375839</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101375901</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,8 +1044,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101375928</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>